--- a/data/trans_orig/IQ2606_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R2-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>93497</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84849</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>100253</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>78,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>71,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>101690</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>94102</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108868</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>94592</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>107961</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>80,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>74,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>93497</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85603</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>100216</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>184339</t>
+          <t>184409</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205004</t>
+          <t>205807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -840,67 +840,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>25078</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18322</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33726</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>24000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16822</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31588</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17729</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31098</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>19,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25078</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18359</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32972</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59926</t>
+          <t>59856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118575</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>125690</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>125690</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>125690</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>184880</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>171848</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>197210</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>63,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>172095</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>160787</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>183006</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>160332</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>183697</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>184880</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>171648</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>198296</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339471</t>
+          <t>338898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373620</t>
+          <t>374004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71781</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>97143</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64155</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53244</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>75463</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>52553</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>75918</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,16%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>84111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70695</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97343</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131621</t>
+          <t>131237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165770</t>
+          <t>166343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83543</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72827</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93595</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>89386</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78546</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>99303</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>78592</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98972</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>57,14%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>83543</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>73120</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>93987</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158481</t>
+          <t>157777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187374</t>
+          <t>187276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75028</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64976</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85744</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67048</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57131</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77888</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57462</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>77842</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,86%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75028</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64584</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>85451</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>47,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127631</t>
+          <t>127729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156524</t>
+          <t>157228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>55731</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46898</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67898</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>65264</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55122</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>75664</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>54662</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>75863</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>38,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>55731</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>46641</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>66445</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107221</t>
+          <t>105942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136350</t>
+          <t>135321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123598</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>111431</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>132431</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>106073</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95673</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116215</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>95474</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>116675</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>123598</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>112884</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>132688</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214316</t>
+          <t>215345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243445</t>
+          <t>244724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179329</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179329</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179329</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179329</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179329</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179329</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>417652</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>392687</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>437154</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>428434</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>407089</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>448689</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>404431</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>447552</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>417652</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>395913</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>439847</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>57,57%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>816773</t>
+          <t>811897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>879233</t>
+          <t>874003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>307815</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>288313</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>332780</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>261277</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>241022</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>282622</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>242159</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>285280</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,88%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>307815</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>285620</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>329554</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535945</t>
+          <t>541175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>598405</t>
+          <t>603281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>725467</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>725467</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>725467</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>725467</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>725467</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>725467</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>89411</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81417</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>95827</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>85130</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>76064</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>92372</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>74967</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>91840</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>70,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>89411</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>81700</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>96930</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>76,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163714</t>
+          <t>163695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185408</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27240</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20824</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35234</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35693</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28451</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44759</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28983</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45856</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27240</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19721</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34951</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52066</t>
+          <t>53027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73760</t>
+          <t>73779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>211981</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>200942</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>220748</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>166499</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>156321</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>174629</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>156754</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>175955</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>79,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>211981</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>201702</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>222486</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364707</t>
+          <t>364428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>392266</t>
+          <t>393280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46080</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37313</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>57119</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>44018</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35888</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>54196</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>34562</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53763</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>46080</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>35575</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>56359</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76312</t>
+          <t>75298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>104150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>135867</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>125349</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>145677</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>144001</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>133541</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>153130</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>133217</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>153499</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>76,23%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>135867</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>125199</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>146456</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263266</t>
+          <t>266025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293205</t>
+          <t>294486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,15%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52034</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42224</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>62552</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>44898</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>35769</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55358</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>55682</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,77%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52034</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>41445</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>62702</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83596</t>
+          <t>82315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113535</t>
+          <t>110776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187901</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187901</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187901</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187901</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187901</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103336</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>92226</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>113765</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>65,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>110996</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>100053</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>120937</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>100787</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>121960</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>64,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>57,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>69,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>103336</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>91662</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>114333</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>59,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199504</t>
+          <t>198879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229199</t>
+          <t>230107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70712</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60283</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>81822</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>34,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>47,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>62305</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52364</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>73248</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>51341</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>72514</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>35,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>70712</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>59715</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>82386</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>40,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118149</t>
+          <t>117241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147844</t>
+          <t>148469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>540595</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>519925</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>560415</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>768</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>506627</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>487730</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>526672</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>485312</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>524695</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,05%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>540595</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>520202</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>559587</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1016482</t>
+          <t>1019468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1072821</t>
+          <t>1074166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -4159,67 +4159,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>196066</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>176246</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>216736</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>186913</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>166868</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>205810</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>168845</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>208228</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,95%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>196066</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>177074</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>216459</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>356035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>413719</t>
+          <t>410733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>736661</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>736661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,74 +4616,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10853</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9746</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13063</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11216</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12149</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10801</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12729</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13929</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12202</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14310</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>85,27%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>52</t>
@@ -4691,27 +4691,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27758</t>
+          <t>23638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2536</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,22 +4804,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>893</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>34283</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31169</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34181</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34296</t>
+          <t>27204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41774</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>59291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75388</t>
+          <t>66527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9063</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>965</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3171</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47595</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43028</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50604</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30946</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25654</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35066</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>77,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49735</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44158</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52979</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80681</t>
+          <t>77107</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>69939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86527</t>
+          <t>82602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5698</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2689</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10265</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9061</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4941</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14353</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15243</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60075</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52945</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65221</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41843</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34879</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46366</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>76,96%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>64,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>38028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67428</t>
+          <t>48661</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>103785</t>
+          <t>103952</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95568</t>
+          <t>94316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111274</t>
+          <t>111405</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>27608</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19876</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>131560</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>143923</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>160044</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111389</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>125669</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>114941</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154849</t>
+          <t>107006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172418</t>
+          <t>121901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>267748</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272672</t>
+          <t>255275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>293736</t>
+          <t>278403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25559</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18321</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34442</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>23243</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16801</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31081</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>17015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61568</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>142470</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138916</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334240</t>
+          <t>317281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
